--- a/public/exports-with-coowners/70960516.xlsx
+++ b/public/exports-with-coowners/70960516.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-with-coowners/70960516.xlsx
+++ b/public/exports-with-coowners/70960516.xlsx
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 8</t>
+          <t xml:space="preserve">Ulvemosen 5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1251,16 +1251,16 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">1310679</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J17">
-        <v>2800</v>
+        <v>304</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1316,26 +1316,26 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulvemosen 5</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310679</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J18">
-        <v>304</v>
+        <v>600</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1406,11 +1406,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J19">
-        <v>600</v>
+        <v>454</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Ådalsparkvej 4E</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1481,11 +1481,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J20">
-        <v>454</v>
+        <v>294</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1541,45 +1541,45 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 4E</t>
+          <t xml:space="preserve">Rungsted Havn 8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">2381217, 100749912</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J21">
-        <v>294</v>
+        <v>363</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100144275</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BygTechA/S</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-10</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 8</t>
+          <t xml:space="preserve">Stadionalle 7A</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1626,30 +1626,30 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381217, 100749912</t>
+          <t xml:space="preserve">717973, 2370957</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J22">
-        <v>363</v>
+        <v>3096</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">100144275</t>
+          <t xml:space="preserve">200052253</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BygTechA/S</t>
+          <t xml:space="preserve">LuVa Consult APS</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-10</t>
+          <t xml:space="preserve">2021-08-23</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 7A</t>
+          <t xml:space="preserve">Stadionalle 9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1701,20 +1701,20 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">717973, 2370957</t>
+          <t xml:space="preserve">717970, 2370954</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J23">
-        <v>3096</v>
+        <v>4496</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052253</t>
+          <t xml:space="preserve">200056359</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-23</t>
+          <t xml:space="preserve">2021-12-30</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 9</t>
+          <t xml:space="preserve">Rungsted Havn 32</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1776,30 +1776,30 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">717970, 2370954</t>
+          <t xml:space="preserve">717952, 2381218</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J24">
-        <v>4496</v>
+        <v>476</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056359</t>
+          <t xml:space="preserve">311065041</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuVa Consult APS</t>
+          <t xml:space="preserve">CONSU bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-30</t>
+          <t xml:space="preserve">2024-07-16</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 32</t>
+          <t xml:space="preserve">Rungsted Havn 34</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1851,40 +1851,40 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">717952, 2381218</t>
+          <t xml:space="preserve">717938, 7644227</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J25">
-        <v>476</v>
+        <v>303</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311065041</t>
+          <t xml:space="preserve">311217548</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSU bygningsrådgivning ApS</t>
+          <t xml:space="preserve">BF Byggeservice ApS</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-07-16</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1916,40 +1916,40 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 34</t>
+          <t xml:space="preserve">Alsvej 83</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">717938, 7644227</t>
+          <t xml:space="preserve">2368570</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J26">
-        <v>303</v>
+        <v>341</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217548</t>
+          <t xml:space="preserve">311239833</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">BF Byggeservice ApS</t>
+          <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2006,11 +2006,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J27">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alsvej 83</t>
+          <t xml:space="preserve">Sdr. Jagtvej 10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2076,20 +2076,20 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2368570</t>
+          <t xml:space="preserve">2367182</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J28">
-        <v>393</v>
+        <v>769</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239833</t>
+          <t xml:space="preserve">311259590</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-07</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2141,30 +2141,30 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr. Jagtvej 10</t>
+          <t xml:space="preserve">Stadionalle 11B</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367182</t>
+          <t xml:space="preserve">9153682</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J29">
-        <v>769</v>
+        <v>4057</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259590</t>
+          <t xml:space="preserve">311259593</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 11B</t>
+          <t xml:space="preserve">Usserød Kongevej 45</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">2367843</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J30">
-        <v>4057</v>
+        <v>458</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259593</t>
+          <t xml:space="preserve">311259586</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Usserød Kongevej 45</t>
+          <t xml:space="preserve">Ahornvej 50A</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367843</t>
+          <t xml:space="preserve">2367722</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2310,11 +2310,11 @@
         </is>
       </c>
       <c r="J31">
-        <v>458</v>
+        <v>368</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259586</t>
+          <t xml:space="preserve">311265087</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50A</t>
+          <t xml:space="preserve">Ahornvej 50B</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2381,11 +2381,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J32">
-        <v>368</v>
+        <v>669</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50B</t>
+          <t xml:space="preserve">Ahornvej 50C</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2456,11 +2456,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J33">
-        <v>669</v>
+        <v>500</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2516,30 +2516,30 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50C</t>
+          <t xml:space="preserve">Stadionalle 11A</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367722</t>
+          <t xml:space="preserve">9153682</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J34">
-        <v>500</v>
+        <v>6610</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265087</t>
+          <t xml:space="preserve">311265094</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 11A</t>
+          <t xml:space="preserve">Stadionalle 5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2606,15 +2606,15 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J35">
-        <v>6610</v>
+        <v>6457</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265094</t>
+          <t xml:space="preserve">311265099</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2681,11 +2681,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J36">
-        <v>6457</v>
+        <v>1595</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2741,30 +2741,30 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 5</t>
+          <t xml:space="preserve">Selmersvej 13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">2366692</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J37">
-        <v>1595</v>
+        <v>613</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265099</t>
+          <t xml:space="preserve">311265957</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-09</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Kommune</t>
+          <t xml:space="preserve">Anne-Mette Casparij</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 13</t>
+          <t xml:space="preserve">Selmersvej 1B</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366692</t>
+          <t xml:space="preserve">250251, 250252, 250253, 250261</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="J38">
-        <v>613</v>
+        <v>386</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265957</t>
+          <t xml:space="preserve">311269737</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">Boligeftersyn P/S</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-30</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anne-Mette Casparij</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 1B</t>
+          <t xml:space="preserve">Rungstedvej 31</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,30 +2901,30 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">250251, 250252, 250253, 250261</t>
+          <t xml:space="preserve">8101069</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J39">
-        <v>386</v>
+        <v>267</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269737</t>
+          <t xml:space="preserve">311269866</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligeftersyn P/S</t>
+          <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-30</t>
+          <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2966,30 +2966,30 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungstedvej 31</t>
+          <t xml:space="preserve">Stadionalle 4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101069</t>
+          <t xml:space="preserve">2381983</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J40">
-        <v>267</v>
+        <v>521</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269866</t>
+          <t xml:space="preserve">311270049</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 4</t>
+          <t xml:space="preserve">Bibliotekstorvet 1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381983</t>
+          <t xml:space="preserve">246772</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,11 +3060,11 @@
         </is>
       </c>
       <c r="J41">
-        <v>521</v>
+        <v>5875</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270049</t>
+          <t xml:space="preserve">311272829</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-31</t>
+          <t xml:space="preserve">2027-09-14</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekstorvet 1</t>
+          <t xml:space="preserve">Kokkedal Stationsvej 3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">246772</t>
+          <t xml:space="preserve">2369157</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3135,11 +3135,11 @@
         </is>
       </c>
       <c r="J42">
-        <v>5875</v>
+        <v>476</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272829</t>
+          <t xml:space="preserve">311272832</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kokkedal Stationsvej 3</t>
+          <t xml:space="preserve">Breeltevej 3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369157</t>
+          <t xml:space="preserve">100019618</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,11 +3210,11 @@
         </is>
       </c>
       <c r="J43">
-        <v>476</v>
+        <v>1306</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272832</t>
+          <t xml:space="preserve">311279819</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-14</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breeltevej 3</t>
+          <t xml:space="preserve">Gasværksvej 1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019618</t>
+          <t xml:space="preserve">2367211</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3285,11 +3285,11 @@
         </is>
       </c>
       <c r="J44">
-        <v>1306</v>
+        <v>430</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279819</t>
+          <t xml:space="preserve">311279821</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 1</t>
+          <t xml:space="preserve">Skovvænget 36</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367211</t>
+          <t xml:space="preserve">2366957</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,11 +3360,11 @@
         </is>
       </c>
       <c r="J45">
-        <v>430</v>
+        <v>744</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279821</t>
+          <t xml:space="preserve">311286269</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 36</t>
+          <t xml:space="preserve">Sophielund 25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366957</t>
+          <t xml:space="preserve">2369150</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3435,11 +3435,11 @@
         </is>
       </c>
       <c r="J46">
-        <v>744</v>
+        <v>1941</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286269</t>
+          <t xml:space="preserve">311286265</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophielund 25</t>
+          <t xml:space="preserve">Rungstedvej 1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369150</t>
+          <t xml:space="preserve">2367324</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3510,11 +3510,11 @@
         </is>
       </c>
       <c r="J47">
-        <v>1941</v>
+        <v>2151</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286265</t>
+          <t xml:space="preserve">311288806</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-29</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungstedvej 1</t>
+          <t xml:space="preserve">Ådalsvej 52</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367324</t>
+          <t xml:space="preserve">2369817</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3585,11 +3585,11 @@
         </is>
       </c>
       <c r="J48">
-        <v>2151</v>
+        <v>1351</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288806</t>
+          <t xml:space="preserve">311288805</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3656,11 +3656,11 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J49">
-        <v>1351</v>
+        <v>1171</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsvej 52</t>
+          <t xml:space="preserve">Selmersvej 6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369817</t>
+          <t xml:space="preserve">8101069</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3735,11 +3735,11 @@
         </is>
       </c>
       <c r="J50">
-        <v>1171</v>
+        <v>1691</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288805</t>
+          <t xml:space="preserve">311289939</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3806,15 +3806,15 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J51">
-        <v>1691</v>
+        <v>3265</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289939</t>
+          <t xml:space="preserve">311289940</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3881,15 +3881,15 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J52">
-        <v>3265</v>
+        <v>1610</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289940</t>
+          <t xml:space="preserve">311289942</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3956,15 +3956,15 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J53">
-        <v>1610</v>
+        <v>2388</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289942</t>
+          <t xml:space="preserve">311289943</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4031,15 +4031,15 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J54">
-        <v>2388</v>
+        <v>474</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289943</t>
+          <t xml:space="preserve">311289945</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 6</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,20 +4101,20 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101069</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J55">
-        <v>474</v>
+        <v>8807</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289945</t>
+          <t xml:space="preserve">311298940</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-21</t>
+          <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4181,11 +4181,11 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J56">
-        <v>8807</v>
+        <v>2450</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4256,15 +4256,15 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J57">
-        <v>2450</v>
+        <v>1637</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298940</t>
+          <t xml:space="preserve">311298938</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4316,30 +4316,30 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">2380704</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J58">
-        <v>1637</v>
+        <v>1507</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298938</t>
+          <t xml:space="preserve">311306137</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-21</t>
+          <t xml:space="preserve">2028-04-03</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 12</t>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">2380704</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="J59">
-        <v>6712</v>
+        <v>2099</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311304707</t>
+          <t xml:space="preserve">311308266</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-23</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4481,15 +4481,15 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J60">
-        <v>1507</v>
+        <v>3262</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306137</t>
+          <t xml:space="preserve">311308262</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-03</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4556,15 +4556,15 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J61">
-        <v>2099</v>
+        <v>614</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308266</t>
+          <t xml:space="preserve">311308267</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4616,40 +4616,40 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Stationsvej 1A</t>
+          <t xml:space="preserve">Ådalsparkvej 4N</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380704</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J62">
-        <v>3262</v>
+        <v>408</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308262</t>
+          <t xml:space="preserve">311420783</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2030-02-04</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Kommune</t>
+          <t xml:space="preserve">Hørsholm Almene Boligselskab</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4691,40 +4691,40 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Stationsvej 1A</t>
+          <t xml:space="preserve">Sophielund 88</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380704</t>
+          <t xml:space="preserve">247821, 247822</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J63">
-        <v>614</v>
+        <v>3028</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308267</t>
+          <t xml:space="preserve">311623696</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2032-08-29</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Kommune</t>
+          <t xml:space="preserve">Hørsholm Almene Boligselskab</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 4N</t>
+          <t xml:space="preserve">Louiselund 2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,30 +4776,30 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">413034, 413035</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J64">
-        <v>408</v>
+        <v>7932</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420783</t>
+          <t xml:space="preserve">311626143</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-04</t>
+          <t xml:space="preserve">2032-09-07</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophielund 88</t>
+          <t xml:space="preserve">Louiselund 7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,20 +4851,20 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">247821, 247822</t>
+          <t xml:space="preserve">413034, 413035</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J65">
-        <v>3028</v>
+        <v>4467</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623696</t>
+          <t xml:space="preserve">311626082</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-29</t>
+          <t xml:space="preserve">2032-09-07</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,30 +4916,30 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Louiselund 2</t>
+          <t xml:space="preserve">Kong Georgsvej 9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2950</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">413034, 413035</t>
+          <t xml:space="preserve">246868, 246869</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J66">
-        <v>7932</v>
+        <v>2508</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626143</t>
+          <t xml:space="preserve">311626489</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-07</t>
+          <t xml:space="preserve">2032-09-08</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Almene Boligselskab</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Louiselund 7</t>
+          <t xml:space="preserve">Rungstedvej 23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,30 +5001,30 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">413034, 413035</t>
+          <t xml:space="preserve">2366696</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J67">
-        <v>4467</v>
+        <v>445</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626082</t>
+          <t xml:space="preserve">311892520</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-07</t>
+          <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Almene Boligselskab</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5066,17 +5066,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Georgsvej 9</t>
+          <t xml:space="preserve">Hørsholm Alle 4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2950</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">246868, 246869</t>
+          <t xml:space="preserve">2367940</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="J68">
-        <v>2508</v>
+        <v>350</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626489</t>
+          <t xml:space="preserve">311893229</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-08</t>
+          <t xml:space="preserve">2036-04-10</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungstedvej 23</t>
+          <t xml:space="preserve">Hørsholm Alle 4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,20 +5151,20 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366696</t>
+          <t xml:space="preserve">2367940</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J69">
-        <v>445</v>
+        <v>2855</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892520</t>
+          <t xml:space="preserve">311893225</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-08</t>
+          <t xml:space="preserve">2036-04-10</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Alle 4</t>
+          <t xml:space="preserve">Mariehøj Alle 1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367940</t>
+          <t xml:space="preserve">7951098</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="J70">
-        <v>350</v>
+        <v>690</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893229</t>
+          <t xml:space="preserve">311912380</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-10</t>
+          <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Alle 4</t>
+          <t xml:space="preserve">Lundevej 26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,20 +5301,20 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367940</t>
+          <t xml:space="preserve">9153647</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>2855</v>
+        <v>840</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893225</t>
+          <t xml:space="preserve">311915684</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-10</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mariehøj Alle 1</t>
+          <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7951098</t>
+          <t xml:space="preserve">7966206</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,11 +5385,11 @@
         </is>
       </c>
       <c r="J72">
-        <v>690</v>
+        <v>1343</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912380</t>
+          <t xml:space="preserve">311916600</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-02</t>
+          <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 26</t>
+          <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,20 +5451,20 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153647</t>
+          <t xml:space="preserve">7966206</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J73">
-        <v>840</v>
+        <v>929</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915684</t>
+          <t xml:space="preserve">311916600</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J74">
-        <v>1343</v>
+        <v>2007</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5606,11 +5606,11 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J75">
-        <v>929</v>
+        <v>599</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5681,11 +5681,11 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J76">
-        <v>2007</v>
+        <v>3389</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Byvej 10</t>
+          <t xml:space="preserve">Lundevej 19</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5756,11 +5756,11 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J77">
-        <v>599</v>
+        <v>2456</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5816,30 +5816,30 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Byvej 10</t>
+          <t xml:space="preserve">Stadionalle 12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966206</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J78">
-        <v>3389</v>
+        <v>6712</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916600</t>
+          <t xml:space="preserve">311931619</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-30</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,30 +5891,30 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 19</t>
+          <t xml:space="preserve">Stadionalle 8</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966206</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J79">
-        <v>2456</v>
+        <v>2800</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916600</t>
+          <t xml:space="preserve">311931619</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-30</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
